--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.71387780050895</v>
+        <v>7.916005142582704</v>
       </c>
       <c r="D2" t="n">
-        <v>49.38923528968634</v>
+        <v>8.02575073457403</v>
       </c>
       <c r="E2" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F2" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.7781424549996</v>
+        <v>3.376448148937435</v>
       </c>
       <c r="D3" t="n">
-        <v>19.90524515604421</v>
+        <v>3.234602337857184</v>
       </c>
       <c r="E3" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F3" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.82932631250584</v>
+        <v>7.284765525782199</v>
       </c>
       <c r="D4" t="n">
-        <v>45.63398022949443</v>
+        <v>7.415521787292846</v>
       </c>
       <c r="E4" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F4" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.79277746882337</v>
+        <v>1.753826338683797</v>
       </c>
       <c r="D5" t="n">
-        <v>10.87612212679517</v>
+        <v>1.767369845604215</v>
       </c>
       <c r="E5" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F5" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.35414389292139</v>
+        <v>6.882548382599727</v>
       </c>
       <c r="D6" t="n">
-        <v>42.92529608788728</v>
+        <v>6.975360614281683</v>
       </c>
       <c r="E6" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F6" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.84630685073581</v>
+        <v>5.012524863244569</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20810286491114</v>
+        <v>5.07131671554806</v>
       </c>
       <c r="E7" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F7" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.71537090951727</v>
+        <v>2.391247772796557</v>
       </c>
       <c r="D8" t="n">
-        <v>13.08186369862576</v>
+        <v>2.125802851026686</v>
       </c>
       <c r="E8" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F8" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.82378519712454</v>
+        <v>4.521365094532737</v>
       </c>
       <c r="D9" t="n">
-        <v>26.81355146454241</v>
+        <v>4.357202112988142</v>
       </c>
       <c r="E9" t="n">
-        <v>13.30265007441477</v>
+        <v>2.1616806370924</v>
       </c>
       <c r="F9" t="n">
-        <v>13.93236643262395</v>
+        <v>2.264009545301392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
